--- a/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_bladder_cancer_dietary.xlsx
+++ b/sources/metaPee/combined/provisional_ui/subexposure_views/yes/Plot/exposures_meta_analysis_bladder_cancer_dietary.xlsx
@@ -883,106 +883,106 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dairy</t>
+          <t>whole_grain_intake</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v>0.7202909870050258</v>
+        <v>0.7226718735643111</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>0.5350473667627881</v>
+        <v>0.5177307290339085</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>0.9696694875814453</v>
+        <v>1.008737954989623</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.2778060956973245</v>
+        <v>0.01658634469437209</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>1.867558394132354</v>
+        <v>31.48702420360033</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I14" s="5" t="inlineStr"/>
       <c r="J14" s="2" t="n">
-        <v>307578</v>
+        <v>219042</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>3968</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>whole_grain_intake</t>
+          <t>folic_acid</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v>0.7226718735643111</v>
+        <v>0.7311036772103915</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>0.5177307290339085</v>
+        <v>0.5091055075111857</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1.008737954989623</v>
+        <v>1.049905331889996</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.01658634469437209</v>
+        <v>0.1542791183442667</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>31.48702420360033</v>
+        <v>3.4645815491233</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I15" s="5" t="inlineStr"/>
       <c r="J15" s="2" t="n">
-        <v>219042</v>
+        <v>307597</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1666</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>folic_acid</t>
+          <t>dairy</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.7311036772103915</v>
+        <v>0.7336670233195703</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.5091055075111857</v>
+        <v>0.5325385444896668</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>1.049905331889996</v>
+        <v>1.010757449721169</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.1542791183442667</v>
+        <v>0.2667027912984513</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.4645815491233</v>
+        <v>2.018228974980078</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I16" s="5" t="inlineStr"/>
       <c r="J16" s="2" t="n">
-        <v>307597</v>
+        <v>306953</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>1465</v>
+        <v>3788</v>
       </c>
     </row>
     <row r="17">
@@ -1023,86 +1023,86 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>vitamin_c</t>
+          <t>non_nutritive_sweetener_intake</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v>0.7509621709935039</v>
+        <v>0.7504264322028401</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>0.5556037048097945</v>
+        <v>0.5305667184532947</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>1.014910062303704</v>
-      </c>
-      <c r="F18" s="3" t="n">
-        <v>0.05110412975560341</v>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v>11.03519783939657</v>
-      </c>
+        <v>1.059855422172594</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr"/>
+      <c r="G18" s="3" t="inlineStr"/>
       <c r="H18" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I18" s="5" t="inlineStr"/>
       <c r="J18" s="2" t="n">
-        <v>8606</v>
+        <v>80388</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>902</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>vitamin_c</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v>0.7692032808507674</v>
+        <v>0.7509621709935039</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>0.3929393518554822</v>
+        <v>0.5556037048097945</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>1.505612812937899</v>
-      </c>
-      <c r="F19" s="3" t="inlineStr"/>
-      <c r="G19" s="3" t="inlineStr"/>
+        <v>1.014910062303704</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>0.05110412975560341</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>11.03519783939657</v>
+      </c>
       <c r="H19" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="5" t="inlineStr"/>
       <c r="J19" s="2" t="n">
-        <v>121519</v>
+        <v>8606</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>737</v>
+        <v>902</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vitamin_b12</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.7708048744499005</v>
+        <v>0.7692032808507674</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.6110819817568988</v>
+        <v>0.3929393518554822</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.990044948040641</v>
+        <v>1.505612812937899</v>
       </c>
       <c r="F20" s="3" t="inlineStr"/>
       <c r="G20" s="3" t="inlineStr"/>
@@ -1111,29 +1111,29 @@
       </c>
       <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="2" t="n">
-        <v>2589</v>
+        <v>121519</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>1171</v>
+        <v>737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>avocado</t>
+          <t>vitamin_b12</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0.7773224664291063</v>
+        <v>0.7708048744499005</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0.5959491108750986</v>
+        <v>0.6110819817568988</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>1.013794275030678</v>
+        <v>0.990044948040641</v>
       </c>
       <c r="F21" s="3" t="inlineStr"/>
       <c r="G21" s="3" t="inlineStr"/>
@@ -1142,29 +1142,29 @@
       </c>
       <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="2" t="n">
-        <v>112328</v>
+        <v>2589</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>1165</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>insoluble_dietary_fiber_intake</t>
+          <t>avocado</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>0.8303208655186842</v>
+        <v>0.7773224664291063</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>0.6705029098644103</v>
+        <v>0.5959491108750986</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>1.029929753803904</v>
+        <v>1.013794275030678</v>
       </c>
       <c r="F22" s="3" t="inlineStr"/>
       <c r="G22" s="3" t="inlineStr"/>
@@ -1173,29 +1173,29 @@
       </c>
       <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="2" t="n">
-        <v>101721</v>
+        <v>112328</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>776</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>plant_protein_intake</t>
+          <t>insoluble_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.8387018493286374</v>
+        <v>0.8303208655186842</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.7048290414313586</v>
+        <v>0.6705029098644103</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.9981018038573761</v>
+        <v>1.029929753803904</v>
       </c>
       <c r="F23" s="3" t="inlineStr"/>
       <c r="G23" s="3" t="inlineStr"/>
@@ -1204,29 +1204,29 @@
       </c>
       <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="2" t="n">
-        <v>585408</v>
+        <v>101721</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>2402</v>
+        <v>776</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>total_dietary_fiber_intake</t>
+          <t>plant_protein_intake</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
         <v>2</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v>0.8530816628701524</v>
+        <v>0.8387018493286374</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.7636085425406669</v>
+        <v>0.7048290414313586</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>0.9529431793814942</v>
+        <v>0.9981018038573761</v>
       </c>
       <c r="F24" s="3" t="inlineStr"/>
       <c r="G24" s="3" t="inlineStr"/>
@@ -1235,29 +1235,29 @@
       </c>
       <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="2" t="n">
-        <v>676447</v>
+        <v>585408</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3990</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>soluble_dietary_fiber_intake</t>
+          <t>total_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v>0.86027378065949</v>
+        <v>0.8530816628701524</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>0.6804949413246006</v>
+        <v>0.7636085425406669</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1.079803598340883</v>
+        <v>0.9529431793814942</v>
       </c>
       <c r="F25" s="3" t="inlineStr"/>
       <c r="G25" s="3" t="inlineStr"/>
@@ -1266,80 +1266,76 @@
       </c>
       <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="2" t="n">
-        <v>101721</v>
+        <v>676447</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>776</v>
+        <v>3990</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>vitamin_e</t>
+          <t>soluble_dietary_fiber_intake</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.8602777300074131</v>
+        <v>0.86027378065949</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>0.6890785559681998</v>
+        <v>0.6804949413246006</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>1.074010744256656</v>
-      </c>
-      <c r="F26" s="3" t="n">
-        <v>0.5285804357154186</v>
-      </c>
-      <c r="G26" s="3" t="n">
-        <v>1.400123278768412</v>
-      </c>
+        <v>1.079803598340883</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr"/>
+      <c r="G26" s="3" t="inlineStr"/>
       <c r="H26" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I26" s="5" t="inlineStr"/>
       <c r="J26" s="2" t="n">
-        <v>157524</v>
+        <v>101721</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>1453</v>
+        <v>776</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>beta_carotene</t>
+          <t>vitamin_e</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.8823204208528399</v>
+        <v>0.8602777300074131</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.7072295387051121</v>
+        <v>0.6890785559681998</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.100648993591191</v>
+        <v>1.074010744256656</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.4501580331890584</v>
+        <v>0.5285804357154186</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>1.72936894969723</v>
+        <v>1.400123278768412</v>
       </c>
       <c r="H27" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="2" t="n">
-        <v>366541</v>
+        <v>157524</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1449</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="28">
@@ -1349,22 +1345,22 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v>0.8879853800794423</v>
+        <v>0.8820557644270329</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>0.7699728688614912</v>
+        <v>0.7588888158485086</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>1.02398307688371</v>
+        <v>1.025212594138781</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5521071094008609</v>
+        <v>0.5369416697280761</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>1.428197575811912</v>
+        <v>1.448988624691713</v>
       </c>
       <c r="H28" s="4" t="n">
         <v>0</v>
@@ -1374,92 +1370,92 @@
         <v>1002741</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>9455</v>
+        <v>9130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>monounsaturated_fat_mufa</t>
+          <t>beta_carotene</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.9462958698523343</v>
+        <v>0.8823204208528399</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.436660182850176</v>
+        <v>0.7072295387051121</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>2.050943641160259</v>
-      </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
+        <v>1.100648993591191</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>0.4501580331890584</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>1.72936894969723</v>
+      </c>
       <c r="H29" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="2" t="n">
-        <v>648914</v>
+        <v>366541</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>3592</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>tea</t>
+          <t>mediterranean_diet</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>0.9617507091463667</v>
+        <v>0.8902226072035401</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>0.7890701910914995</v>
+        <v>0.6205359319277568</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>1.172337946680718</v>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.5117552101281551</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>1.807435289836927</v>
-      </c>
+        <v>1.259255513560131</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr"/>
+      <c r="G30" s="3" t="inlineStr"/>
       <c r="H30" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="2" t="n">
-        <v>580076</v>
+        <v>37442</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>9039</v>
+        <v>379</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>mediterranean_diet</t>
+          <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0.9700661602031396</v>
+        <v>0.9462958698523343</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.8802401192762667</v>
+        <v>0.436660182850176</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.079803598340883</v>
+        <v>2.050943641160259</v>
       </c>
       <c r="F31" s="3" t="inlineStr"/>
       <c r="G31" s="3" t="inlineStr"/>
@@ -1468,126 +1464,130 @@
       </c>
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>37442</v>
+        <v>648914</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>379</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>non_nutritive_sweetener_intake</t>
+          <t>tea</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>0.9900225074278087</v>
+        <v>0.9617507091463667</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.7803902529973801</v>
+        <v>0.7890701910914995</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>1.259255513560131</v>
-      </c>
-      <c r="F32" s="3" t="inlineStr"/>
-      <c r="G32" s="3" t="inlineStr"/>
+        <v>1.172337946680718</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.5117552101281551</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>1.807435289836927</v>
+      </c>
       <c r="H32" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>80388</v>
+        <v>580076</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>448</v>
+        <v>9039</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>vitamin_b1</t>
+          <t>phosphorus</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1.026135700809198</v>
+        <v>0.9740428329225616</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.8760781322122511</v>
+        <v>0.2712267749764213</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>1.201895627523871</v>
-      </c>
-      <c r="F33" s="3" t="n">
-        <v>0.1861215877235062</v>
-      </c>
-      <c r="G33" s="3" t="n">
-        <v>5.657347378958563</v>
-      </c>
+        <v>3.498030164795818</v>
+      </c>
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>575001</v>
+        <v>1147</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>3737</v>
+        <v>522</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>iron</t>
+          <t>vitamin_b1</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.049880653285851</v>
+        <v>1.026135700809198</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0.9900225074278087</v>
+        <v>0.8760781322122511</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.119694504834913</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+        <v>1.201895627523871</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.1861215877235062</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>5.657347378958563</v>
+      </c>
       <c r="H34" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="2" t="n">
-        <v>481419</v>
+        <v>575001</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>1001</v>
+        <v>3737</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>lycopene</t>
+          <t>iron</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.053375742513365</v>
+        <v>1.049880653285851</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>0.8658011636136935</v>
+        <v>0.9900225074278087</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>1.281588084594754</v>
+        <v>1.119694504834913</v>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
@@ -1596,95 +1596,95 @@
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>222535</v>
+        <v>481419</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>1249</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>lycopene</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.086433159799911</v>
+        <v>1.053375742513365</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.9792189645694596</v>
+        <v>0.8658011636136935</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>1.205265651112213</v>
-      </c>
-      <c r="F36" s="3" t="n">
-        <v>0.8385628597437634</v>
-      </c>
-      <c r="G36" s="3" t="n">
-        <v>1.407571295339136</v>
-      </c>
+        <v>1.281588084594754</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
       <c r="H36" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>938913</v>
+        <v>222535</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>6956</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>western_pattern_diet</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.089777005663733</v>
+        <v>1.086433159799911</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0.86027378065949</v>
+        <v>0.9792189645694596</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>1.378808493040073</v>
-      </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
+        <v>1.205265651112213</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.8385628597437634</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>1.407571295339136</v>
+      </c>
       <c r="H37" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>388077</v>
+        <v>938913</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>822</v>
+        <v>6956</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sugar_sweetened_beverage_intake</t>
+          <t>western_pattern_diet</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1.109722458890099</v>
+        <v>1.089777005663733</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.009977038572974</v>
+        <v>0.86027378065949</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>1.219390011363415</v>
+        <v>1.378808493040073</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr"/>
@@ -1693,29 +1693,29 @@
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>73024</v>
+        <v>388077</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>297</v>
+        <v>822</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lutein</t>
+          <t>sugar_sweetened_beverage_intake</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1.11</v>
+        <v>1.109722458890099</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>0.79</v>
+        <v>1.009977038572974</v>
       </c>
       <c r="E39" s="3" t="n">
-        <v>1.57</v>
+        <v>1.219390011363415</v>
       </c>
       <c r="F39" s="3" t="inlineStr"/>
       <c r="G39" s="3" t="inlineStr"/>
@@ -1724,29 +1724,29 @@
       </c>
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="2" t="n">
-        <v>120852</v>
+        <v>73024</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>475</v>
+        <v>297</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>dietary_protein_intake</t>
+          <t>lutein</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v>1.117841954220713</v>
+        <v>1.11</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>1.012983563938329</v>
+        <v>0.79</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>1.233678059956743</v>
+        <v>1.57</v>
       </c>
       <c r="F40" s="3" t="inlineStr"/>
       <c r="G40" s="3" t="inlineStr"/>
@@ -1755,45 +1755,41 @@
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="2" t="n">
-        <v>585408</v>
+        <v>120852</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2402</v>
+        <v>475</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>soy</t>
+          <t>dietary_protein_intake</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C41" s="3" t="n">
-        <v>1.121536926019923</v>
+        <v>1.117841954220713</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.3146796946098465</v>
+        <v>1.012983563938329</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>3.99722351957202</v>
-      </c>
-      <c r="F41" s="3" t="n">
-        <v>2.372968668867597e-07</v>
-      </c>
-      <c r="G41" s="3" t="n">
-        <v>5300723.490068127</v>
-      </c>
+        <v>1.233678059956743</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
       <c r="H41" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="2" t="n">
-        <v>49061</v>
+        <v>585408</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>222</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="42">
@@ -1861,20 +1857,20 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>phosphorus</t>
+          <t>tomato</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C44" s="3" t="n">
-        <v>1.193750462204806</v>
+        <v>1.19945453907786</v>
       </c>
       <c r="D44" s="3" t="n">
-        <v>0.473548946499235</v>
+        <v>0.9501079967336835</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>3.009277449668003</v>
+        <v>1.518204486493061</v>
       </c>
       <c r="F44" s="3" t="inlineStr"/>
       <c r="G44" s="3" t="inlineStr"/>
@@ -1883,76 +1879,76 @@
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="2" t="n">
-        <v>1147</v>
+        <v>101683</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>522</v>
+        <v>774</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>tomato</t>
+          <t>red_meat</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.19945453907786</v>
+        <v>1.32154300883515</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>0.9501079967336835</v>
+        <v>1.111710699877804</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>1.518204486493061</v>
-      </c>
-      <c r="F45" s="3" t="inlineStr"/>
-      <c r="G45" s="3" t="inlineStr"/>
+        <v>1.570980583701342</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>0.7815874035063086</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>2.234524144537296</v>
+      </c>
       <c r="H45" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="2" t="n">
-        <v>101683</v>
+        <v>1417360</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>774</v>
+        <v>6876</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>soy</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.32154300883515</v>
+        <v>1.508325356558058</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1.111710699877804</v>
+        <v>0.1884919459617998</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.570980583701342</v>
-      </c>
-      <c r="F46" s="3" t="n">
-        <v>0.7815874035063086</v>
-      </c>
-      <c r="G46" s="3" t="n">
-        <v>2.234524144537296</v>
-      </c>
+        <v>12.0697219694313</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr"/>
+      <c r="G46" s="3" t="inlineStr"/>
       <c r="H46" s="4" t="n">
         <v>0</v>
       </c>
       <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="2" t="n">
-        <v>1417360</v>
+        <v>32477</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>6876</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47">
